--- a/INPUT/CxC al 27.03.2026.xlsx
+++ b/INPUT/CxC al 27.03.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodrigom\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xitanium\Downloads\INPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2975BD18-6A6B-4720-B5AB-9F26FEB37C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B8E12F-F264-45DA-97C8-B8BEC8FFC210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="2" r:id="rId1"/>
@@ -23,19 +23,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="38" r:id="rId5"/>
-    <pivotCache cacheId="39" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -4215,7 +4211,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F23B146-7780-4C1D-8814-B57F365C1358}" name="TablaDinámica2" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8F23B146-7780-4C1D-8814-B57F365C1358}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:N18" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -4469,7 +4465,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD10559E-A6E4-491D-BF55-A8D147B7C22E}" name="TablaDinámica1" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD10559E-A6E4-491D-BF55-A8D147B7C22E}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField showAll="0"/>
@@ -4831,559 +4827,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78C9CAC0-25A5-4DBD-9091-74FD25655C81}" name="TablaDinámica4" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="F18:I19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="21">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="77">
-        <item m="1" x="68"/>
-        <item x="29"/>
-        <item m="1" x="71"/>
-        <item m="1" x="74"/>
-        <item m="1" x="75"/>
-        <item m="1" x="72"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item m="1" x="69"/>
-        <item m="1" x="70"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="57"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="59"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="28"/>
-        <item m="1" x="73"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="30"/>
-        <item x="58"/>
-        <item x="54"/>
-        <item x="39"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="49"/>
-        <item x="62"/>
-        <item x="27"/>
-        <item x="40"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item h="1" x="4"/>
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="3" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="4" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="34"/>
-        <item x="31"/>
-        <item x="26"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="19"/>
-        <item x="28"/>
-        <item x="20"/>
-        <item x="33"/>
-        <item x="29"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="32"/>
-        <item x="14"/>
-        <item m="1" x="35"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="21"/>
-        <item x="30"/>
-        <item x="15"/>
-        <item x="11"/>
-        <item x="24"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item h="1" x="1"/>
-        <item h="1" m="1" x="4"/>
-        <item m="1" x="3"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="1">
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="4" hier="-1"/>
-    <pageField fld="17" hier="-1"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Suma de DÍAS VENCIDOS" fld="12" baseField="0" baseItem="0"/>
-    <dataField name="Suma de DÍAS ATRASADOS" fld="16" baseField="0" baseItem="0"/>
-    <dataField name="Suma de USD HOMOL" fld="15" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{12D76F04-516E-4F5F-93F1-491515CEABED}" name="TablaDinámica3" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="F4:I7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="21">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="21">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="77">
-        <item m="1" x="68"/>
-        <item x="29"/>
-        <item m="1" x="71"/>
-        <item m="1" x="74"/>
-        <item m="1" x="75"/>
-        <item m="1" x="72"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item m="1" x="69"/>
-        <item m="1" x="70"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="57"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="59"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="28"/>
-        <item m="1" x="73"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="30"/>
-        <item x="58"/>
-        <item x="54"/>
-        <item x="39"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="49"/>
-        <item x="62"/>
-        <item x="27"/>
-        <item x="40"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item h="1" x="4"/>
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="3" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="4" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="34"/>
-        <item x="31"/>
-        <item x="26"/>
-        <item x="22"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="19"/>
-        <item x="28"/>
-        <item x="20"/>
-        <item x="33"/>
-        <item x="29"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="32"/>
-        <item x="14"/>
-        <item m="1" x="35"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="25"/>
-        <item x="10"/>
-        <item x="21"/>
-        <item x="30"/>
-        <item x="15"/>
-        <item x="11"/>
-        <item x="24"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item h="1" x="1"/>
-        <item m="1" x="4"/>
-        <item h="1" m="1" x="3"/>
-        <item h="1" x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="4" hier="-1"/>
-    <pageField fld="17" hier="-1"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Suma de DÍAS VENCIDOS" fld="12" baseField="0" baseItem="0"/>
-    <dataField name="Suma de DÍAS ATRASADOS" fld="16" baseField="0" baseItem="0"/>
-    <dataField name="Suma de USD HOMOL" fld="15" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFD24885-0E38-462C-9A45-60766236540C}" name="TablaDinámica2" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFD24885-0E38-462C-9A45-60766236540C}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:D35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="21">
     <pivotField showAll="0"/>
@@ -5700,6 +5144,558 @@
     </i>
     <i r="1">
       <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="4" hier="-1"/>
+    <pageField fld="17" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Suma de DÍAS VENCIDOS" fld="12" baseField="0" baseItem="0"/>
+    <dataField name="Suma de DÍAS ATRASADOS" fld="16" baseField="0" baseItem="0"/>
+    <dataField name="Suma de USD HOMOL" fld="15" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78C9CAC0-25A5-4DBD-9091-74FD25655C81}" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F18:I19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="77">
+        <item m="1" x="68"/>
+        <item x="29"/>
+        <item m="1" x="71"/>
+        <item m="1" x="74"/>
+        <item m="1" x="75"/>
+        <item m="1" x="72"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item m="1" x="69"/>
+        <item m="1" x="70"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="57"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="59"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="28"/>
+        <item m="1" x="73"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="30"/>
+        <item x="58"/>
+        <item x="54"/>
+        <item x="39"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="49"/>
+        <item x="62"/>
+        <item x="27"/>
+        <item x="40"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="34"/>
+        <item x="31"/>
+        <item x="26"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="20"/>
+        <item x="33"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="32"/>
+        <item x="14"/>
+        <item m="1" x="35"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="21"/>
+        <item x="30"/>
+        <item x="15"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="1"/>
+        <item h="1" m="1" x="4"/>
+        <item m="1" x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="4" hier="-1"/>
+    <pageField fld="17" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Suma de DÍAS VENCIDOS" fld="12" baseField="0" baseItem="0"/>
+    <dataField name="Suma de DÍAS ATRASADOS" fld="16" baseField="0" baseItem="0"/>
+    <dataField name="Suma de USD HOMOL" fld="15" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{12D76F04-516E-4F5F-93F1-491515CEABED}" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F4:I7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="77">
+        <item m="1" x="68"/>
+        <item x="29"/>
+        <item m="1" x="71"/>
+        <item m="1" x="74"/>
+        <item m="1" x="75"/>
+        <item m="1" x="72"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item m="1" x="69"/>
+        <item m="1" x="70"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="57"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="59"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="28"/>
+        <item m="1" x="73"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="30"/>
+        <item x="58"/>
+        <item x="54"/>
+        <item x="39"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="49"/>
+        <item x="62"/>
+        <item x="27"/>
+        <item x="40"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="4"/>
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="34"/>
+        <item x="31"/>
+        <item x="26"/>
+        <item x="22"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="19"/>
+        <item x="28"/>
+        <item x="20"/>
+        <item x="33"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="32"/>
+        <item x="14"/>
+        <item m="1" x="35"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="10"/>
+        <item x="21"/>
+        <item x="30"/>
+        <item x="15"/>
+        <item x="11"/>
+        <item x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="1"/>
+        <item m="1" x="4"/>
+        <item h="1" m="1" x="3"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -6063,27 +6059,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BED3E3-ADC2-47AB-9EAF-8216BB4103F8}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>181</v>
       </c>
@@ -6091,7 +6087,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>193</v>
       </c>
@@ -6099,7 +6095,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>215</v>
       </c>
@@ -6125,7 +6121,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>192</v>
       </c>
@@ -6154,7 +6150,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>189</v>
       </c>
@@ -6198,7 +6194,7 @@
         <v>2412657.5700000003</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>39</v>
       </c>
@@ -6224,7 +6220,7 @@
         <v>1066950</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>63</v>
       </c>
@@ -6246,7 +6242,7 @@
         <v>-15658</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>73</v>
       </c>
@@ -6270,7 +6266,7 @@
         <v>77585</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>79</v>
       </c>
@@ -6294,7 +6290,7 @@
         <v>53862.5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>101</v>
       </c>
@@ -6318,7 +6314,7 @@
         <v>147743.07</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>104</v>
       </c>
@@ -6340,7 +6336,7 @@
         <v>-43000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>117</v>
       </c>
@@ -6366,7 +6362,7 @@
         <v>124440</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>137</v>
       </c>
@@ -6394,7 +6390,7 @@
         <v>282040</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>141</v>
       </c>
@@ -6418,7 +6414,7 @@
         <v>31275</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>148</v>
       </c>
@@ -6442,7 +6438,7 @@
         <v>73490</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>166</v>
       </c>
@@ -6472,7 +6468,7 @@
         <v>613930</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>194</v>
       </c>
@@ -6525,7 +6521,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:R73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2" outlineLevelRow="2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12.75" outlineLevelRow="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" customWidth="1"/>
@@ -6538,17 +6534,17 @@
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="26" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="19.109375" customWidth="1"/>
-    <col min="15" max="15" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" customWidth="1"/>
-    <col min="18" max="18" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="19.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>177</v>
       </c>
@@ -6604,7 +6600,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="2" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6649,7 +6645,7 @@
         <v>12.217428817946505</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -6694,7 +6690,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6739,7 +6735,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -6784,7 +6780,7 @@
         <v>8.1449525452976701</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -6829,7 +6825,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -6874,7 +6870,7 @@
         <v>8.1449525452976701</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -6919,7 +6915,7 @@
         <v>12.217428817946505</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -6964,7 +6960,7 @@
         <v>12.217428817946505</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -7009,7 +7005,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -7054,7 +7050,7 @@
         <v>8.1449525452976701</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -7099,7 +7095,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -7144,7 +7140,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -7189,7 +7185,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -7234,7 +7230,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="16" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -7279,7 +7275,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -7324,7 +7320,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -7369,7 +7365,7 @@
         <v>4.072476272648835</v>
       </c>
     </row>
-    <row r="19" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7429,7 +7425,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -7489,7 +7485,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="21" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -7549,7 +7545,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -7609,7 +7605,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -7669,7 +7665,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -7729,7 +7725,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -7774,7 +7770,7 @@
         <v>122.17428817946507</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -7819,7 +7815,7 @@
         <v>81.449525452976701</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -7864,7 +7860,7 @@
         <v>101.81190681622088</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -7908,7 +7904,7 @@
       <c r="Q28" s="17"/>
       <c r="R28" s="18"/>
     </row>
-    <row r="29" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -7952,7 +7948,7 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="18"/>
     </row>
-    <row r="30" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -7996,7 +7992,7 @@
       <c r="Q30" s="17"/>
       <c r="R30" s="18"/>
     </row>
-    <row r="31" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -8041,7 +8037,7 @@
       <c r="Q31" s="17"/>
       <c r="R31" s="18"/>
     </row>
-    <row r="32" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -8101,7 +8097,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="33" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -8162,7 +8158,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="34" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -8207,7 +8203,7 @@
         <v>66.586137474834629</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -8252,7 +8248,7 @@
         <v>6.7874604544147257</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -8297,7 +8293,7 @@
         <v>72.217428817946512</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>82</v>
       </c>
@@ -8342,7 +8338,7 @@
         <v>13.574920908829451</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -8387,7 +8383,7 @@
         <v>96.042565429968363</v>
       </c>
     </row>
-    <row r="39" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -8432,7 +8428,7 @@
         <v>13.574920908829451</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -8477,7 +8473,7 @@
         <v>105.57089444923785</v>
       </c>
     </row>
-    <row r="41" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -8522,7 +8518,7 @@
         <v>39.027897612884672</v>
       </c>
     </row>
-    <row r="42" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>100</v>
       </c>
@@ -8576,7 +8572,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>103</v>
       </c>
@@ -8625,7 +8621,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>103</v>
       </c>
@@ -8674,7 +8670,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="45" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>106</v>
       </c>
@@ -8719,7 +8715,7 @@
         <v>403.58354903652577</v>
       </c>
     </row>
-    <row r="46" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -8764,7 +8760,7 @@
         <v>40.72476272648835</v>
       </c>
     </row>
-    <row r="47" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>106</v>
       </c>
@@ -8809,7 +8805,7 @@
         <v>343.17515099223471</v>
       </c>
     </row>
-    <row r="48" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>106</v>
       </c>
@@ -8854,7 +8850,7 @@
         <v>30.543572044866266</v>
       </c>
     </row>
-    <row r="49" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>116</v>
       </c>
@@ -8914,7 +8910,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>116</v>
       </c>
@@ -8974,7 +8970,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="51" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>116</v>
       </c>
@@ -9034,7 +9030,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="52" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>116</v>
       </c>
@@ -9094,7 +9090,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>124</v>
       </c>
@@ -9139,7 +9135,7 @@
         <v>1282.7149841817659</v>
       </c>
     </row>
-    <row r="54" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>124</v>
       </c>
@@ -9184,7 +9180,7 @@
         <v>2041.4092608570606</v>
       </c>
     </row>
-    <row r="55" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>124</v>
       </c>
@@ -9229,7 +9225,7 @@
         <v>1151.4121368996261</v>
       </c>
     </row>
-    <row r="56" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>124</v>
       </c>
@@ -9274,7 +9270,7 @@
         <v>1425.3666954270923</v>
       </c>
     </row>
-    <row r="57" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>124</v>
       </c>
@@ -9319,7 +9315,7 @@
         <v>1425.3666954270923</v>
       </c>
     </row>
-    <row r="58" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>136</v>
       </c>
@@ -9379,7 +9375,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>136</v>
       </c>
@@ -9434,7 +9430,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>140</v>
       </c>
@@ -9489,7 +9485,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="13.8" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="13.9" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>143</v>
       </c>
@@ -9534,7 +9530,7 @@
         <v>227.20736266896751</v>
       </c>
     </row>
-    <row r="62" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>147</v>
       </c>
@@ -9595,7 +9591,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="63" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>151</v>
       </c>
@@ -9640,7 +9636,7 @@
         <v>169.68651136036814</v>
       </c>
     </row>
-    <row r="64" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>155</v>
       </c>
@@ -9685,7 +9681,7 @@
         <v>191.40638481449525</v>
       </c>
     </row>
-    <row r="65" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>155</v>
       </c>
@@ -9730,7 +9726,7 @@
         <v>35.634167385677308</v>
       </c>
     </row>
-    <row r="66" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>161</v>
       </c>
@@ -9775,7 +9771,7 @@
         <v>16.28990509059534</v>
       </c>
     </row>
-    <row r="67" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>165</v>
       </c>
@@ -9835,7 +9831,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>165</v>
       </c>
@@ -9895,7 +9891,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>165</v>
       </c>
@@ -9955,7 +9951,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="70" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>165</v>
       </c>
@@ -10015,7 +10011,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>165</v>
       </c>
@@ -10071,7 +10067,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="N73" s="12"/>
     </row>
   </sheetData>
@@ -10102,13 +10098,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E2795F-B7FE-42D7-B196-4148D1F5DDA4}">
   <dimension ref="A1:B44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>182</v>
       </c>
@@ -10116,7 +10112,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>187</v>
       </c>
@@ -10124,7 +10120,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>181</v>
       </c>
@@ -10132,7 +10128,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>192</v>
       </c>
@@ -10140,7 +10136,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>39</v>
       </c>
@@ -10148,7 +10144,7 @@
         <v>1066950</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>41</v>
       </c>
@@ -10156,7 +10152,7 @@
         <v>70200</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>45</v>
       </c>
@@ -10164,7 +10160,7 @@
         <v>121500</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>47</v>
       </c>
@@ -10172,7 +10168,7 @@
         <v>173250</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>49</v>
       </c>
@@ -10180,7 +10176,7 @@
         <v>175500</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>51</v>
       </c>
@@ -10188,7 +10184,7 @@
         <v>70200</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>53</v>
       </c>
@@ -10196,7 +10192,7 @@
         <v>456300</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>63</v>
       </c>
@@ -10204,7 +10200,7 @@
         <v>-72403</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>65</v>
       </c>
@@ -10212,7 +10208,7 @@
         <v>-56745</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>68</v>
       </c>
@@ -10220,7 +10216,7 @@
         <v>-15658</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>73</v>
       </c>
@@ -10228,7 +10224,7 @@
         <v>98549</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>77</v>
       </c>
@@ -10236,7 +10232,7 @@
         <v>77585</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>75</v>
       </c>
@@ -10244,7 +10240,7 @@
         <v>20964</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>79</v>
       </c>
@@ -10252,7 +10248,7 @@
         <v>53862.5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>81</v>
       </c>
@@ -10260,7 +10256,7 @@
         <v>53862.5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>101</v>
       </c>
@@ -10268,7 +10264,7 @@
         <v>147743.07</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>203</v>
       </c>
@@ -10276,7 +10272,7 @@
         <v>147743.07</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>104</v>
       </c>
@@ -10284,7 +10280,7 @@
         <v>-43000</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>68</v>
       </c>
@@ -10292,7 +10288,7 @@
         <v>-7410</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>220</v>
       </c>
@@ -10300,7 +10296,7 @@
         <v>-35590</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>117</v>
       </c>
@@ -10308,7 +10304,7 @@
         <v>124440</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>119</v>
       </c>
@@ -10316,7 +10312,7 @@
         <v>12898</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>121</v>
       </c>
@@ -10324,7 +10320,7 @@
         <v>30190</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>218</v>
       </c>
@@ -10332,7 +10328,7 @@
         <v>40616</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>219</v>
       </c>
@@ -10340,7 +10336,7 @@
         <v>40736</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>137</v>
       </c>
@@ -10348,7 +10344,7 @@
         <v>282040</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>204</v>
       </c>
@@ -10356,7 +10352,7 @@
         <v>156680</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>205</v>
       </c>
@@ -10364,7 +10360,7 @@
         <v>125360</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>141</v>
       </c>
@@ -10372,7 +10368,7 @@
         <v>31275</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>206</v>
       </c>
@@ -10380,7 +10376,7 @@
         <v>31275</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>148</v>
       </c>
@@ -10388,7 +10384,7 @@
         <v>73490</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
         <v>150</v>
       </c>
@@ -10396,7 +10392,7 @@
         <v>73490</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>166</v>
       </c>
@@ -10404,7 +10400,7 @@
         <v>613930</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>168</v>
       </c>
@@ -10412,7 +10408,7 @@
         <v>39610</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
         <v>170</v>
       </c>
@@ -10420,7 +10416,7 @@
         <v>94640</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>172</v>
       </c>
@@ -10428,7 +10424,7 @@
         <v>76800</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>174</v>
       </c>
@@ -10436,7 +10432,7 @@
         <v>186880</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
         <v>176</v>
       </c>
@@ -10444,7 +10440,7 @@
         <v>216000</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
         <v>194</v>
       </c>
@@ -10460,24 +10456,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A36BEF-4716-4AFB-BD41-CA71F4FBE23D}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.88671875" customWidth="1"/>
-    <col min="6" max="6" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="18" width="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>181</v>
       </c>
@@ -10491,7 +10487,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>208</v>
       </c>
@@ -10505,7 +10501,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>192</v>
       </c>
@@ -10531,7 +10527,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
@@ -10558,7 +10554,7 @@
         <v>77585</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>41</v>
       </c>
@@ -10585,7 +10581,7 @@
         <v>77585</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>45</v>
       </c>
@@ -10612,7 +10608,7 @@
         <v>77585</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>47</v>
       </c>
@@ -10627,7 +10623,7 @@
       </c>
       <c r="E8" s="14"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>49</v>
       </c>
@@ -10642,7 +10638,7 @@
       </c>
       <c r="E9" s="14"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>51</v>
       </c>
@@ -10657,7 +10653,7 @@
       </c>
       <c r="E10" s="14"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>53</v>
       </c>
@@ -10672,7 +10668,7 @@
       </c>
       <c r="E11" s="14"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>79</v>
       </c>
@@ -10687,7 +10683,7 @@
       </c>
       <c r="E12" s="14"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>81</v>
       </c>
@@ -10702,7 +10698,7 @@
       </c>
       <c r="E13" s="14"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>101</v>
       </c>
@@ -10715,7 +10711,7 @@
       </c>
       <c r="E14" s="14"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>203</v>
       </c>
@@ -10734,7 +10730,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>104</v>
       </c>
@@ -10753,7 +10749,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>117</v>
       </c>
@@ -10768,7 +10764,7 @@
       </c>
       <c r="E17" s="14"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>119</v>
       </c>
@@ -10795,7 +10791,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>121</v>
       </c>
@@ -10816,7 +10812,7 @@
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>218</v>
       </c>
@@ -10831,7 +10827,7 @@
       </c>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>219</v>
       </c>
@@ -10846,7 +10842,7 @@
       </c>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>137</v>
       </c>
@@ -10861,7 +10857,7 @@
       </c>
       <c r="E22" s="14"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>204</v>
       </c>
@@ -10876,7 +10872,7 @@
       </c>
       <c r="E23" s="14"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>205</v>
       </c>
@@ -10889,7 +10885,7 @@
       </c>
       <c r="E24" s="14"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>141</v>
       </c>
@@ -10902,7 +10898,7 @@
       </c>
       <c r="E25" s="14"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>206</v>
       </c>
@@ -10915,7 +10911,7 @@
       </c>
       <c r="E26" s="14"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>148</v>
       </c>
@@ -10930,7 +10926,7 @@
       </c>
       <c r="E27" s="14"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>150</v>
       </c>
@@ -10945,7 +10941,7 @@
       </c>
       <c r="E28" s="14"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>166</v>
       </c>
@@ -10960,7 +10956,7 @@
       </c>
       <c r="E29" s="14"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>168</v>
       </c>
@@ -10975,7 +10971,7 @@
       </c>
       <c r="E30" s="14"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
         <v>170</v>
       </c>
@@ -10990,7 +10986,7 @@
       </c>
       <c r="E31" s="14"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>172</v>
       </c>
@@ -11005,7 +11001,7 @@
       </c>
       <c r="E32" s="14"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>174</v>
       </c>
@@ -11020,7 +11016,7 @@
       </c>
       <c r="E33" s="14"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>176</v>
       </c>
@@ -11033,7 +11029,7 @@
       </c>
       <c r="E34" s="14"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>194</v>
       </c>
@@ -11048,10 +11044,10 @@
       </c>
       <c r="E35" s="14"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E36" s="14"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E37" s="14"/>
     </row>
   </sheetData>
